--- a/Result/checkall/2025-10-10.xlsx
+++ b/Result/checkall/2025-10-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,245 +486,260 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>量倍率</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_收盤價</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_%</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>highlight_date</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LevelArea</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>漲跌BYN天</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>漲跌BYN天Diff</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天Diff</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>VPC_MA_%</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>VPC_break</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change_sum</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>

--- a/Result/checkall/2025-10-10.xlsx
+++ b/Result/checkall/2025-10-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK1"/>
+  <dimension ref="A1:BP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,245 +501,270 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>highlight_%_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>highlight_date</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>LevelArea</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>漲跌BYN天</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>漲跌BYN天Diff</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天Diff</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_date_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_enddate_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_stardate收盤價_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_收盤價_1</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>VPC_MA_%</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>VPC_break</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change_sum</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>

--- a/Result/checkall/2025-10-10.xlsx
+++ b/Result/checkall/2025-10-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP1"/>
+  <dimension ref="A1:BU1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,265 +506,290 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>highlight_%_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>highlight_date</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>LevelArea</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>漲跌BYN天</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>漲跌BYN天Diff</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>增縮BYN天Diff</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>highlight_date_1</t>
-        </is>
-      </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>highlight_enddate_2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_stardate_2</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_enddate收盤價_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_stardate收盤價_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_stardate_1</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate_1</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>highlight_stardate收盤價_1</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>highlight_收盤價_1</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>highlight_enddate收盤價_1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>VPC_MA_%</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>VPC_break</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change_sum</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
